--- a/config/xlsx/game_config.xlsx
+++ b/config/xlsx/game_config.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_config" sheetId="1" r:id="Rbe9ae212438b480e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="game_config" sheetId="1" r:id="R643ff024dcd24f5d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -440,7 +440,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="5" t="str">
-        <x:v>craft_speedup_stone_cost_per_second</x:v>
+        <x:v>craft_speedup_stone_cost_per_minute</x:v>
       </x:c>
       <x:c r="B7" s="5" t="n">
         <x:v>1</x:v>
@@ -448,7 +448,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="5" t="str">
-        <x:v>launcher_speedup_stone_cost_per_second</x:v>
+        <x:v>launcher_speedup_stone_cost_per_minute</x:v>
       </x:c>
       <x:c r="B8" s="5" t="n">
         <x:v>1</x:v>
